--- a/image processing/chapter5.xlsx
+++ b/image processing/chapter5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\PPT\授課版_(教師專用)\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\image processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451ACCD9-1B2E-4AC9-9055-9795EDEEB90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64039F5-B962-4455-95FF-C259E97ABD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="583" windowWidth="24686" windowHeight="13131" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33390" yWindow="-160" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="252">
   <si>
     <t>question</t>
   </si>
@@ -38,630 +38,6 @@
   </si>
   <si>
     <t>answer</t>
-  </si>
-  <si>
-    <t>影像幾何轉換屬於哪種處理方式？</t>
-  </si>
-  <si>
-    <t>像素值處理</t>
-  </si>
-  <si>
-    <t>頻率域處理</t>
-  </si>
-  <si>
-    <t>色彩處理</t>
-  </si>
-  <si>
-    <t>空間位置處理</t>
-  </si>
-  <si>
-    <t>影像平移的特點是？</t>
-  </si>
-  <si>
-    <t>改變影像角度</t>
-  </si>
-  <si>
-    <t>改變影像位置</t>
-  </si>
-  <si>
-    <t>改變像素值</t>
-  </si>
-  <si>
-    <t>改變影像大小</t>
-  </si>
-  <si>
-    <t>影像縮放會改變？</t>
-  </si>
-  <si>
-    <t>像素值</t>
-  </si>
-  <si>
-    <t>影像位置</t>
-  </si>
-  <si>
-    <t>影像角度</t>
-  </si>
-  <si>
-    <t>影像大小</t>
-  </si>
-  <si>
-    <t>影像旋轉會改變？</t>
-  </si>
-  <si>
-    <t>影像方向</t>
-  </si>
-  <si>
-    <t>仿射轉換包括？</t>
-  </si>
-  <si>
-    <t>只有旋轉</t>
-  </si>
-  <si>
-    <t>只有平移</t>
-  </si>
-  <si>
-    <t>只有縮放</t>
-  </si>
-  <si>
-    <t>平移、旋轉、縮放、剪切</t>
-  </si>
-  <si>
-    <t>仿射轉換保持的性質是？</t>
-  </si>
-  <si>
-    <t>平行性</t>
-  </si>
-  <si>
-    <t>距離</t>
-  </si>
-  <si>
-    <t>面積</t>
-  </si>
-  <si>
-    <t>角度</t>
-  </si>
-  <si>
-    <t>透視轉換會改變？</t>
-  </si>
-  <si>
-    <t>只改變位置</t>
-  </si>
-  <si>
-    <t>改變形狀和透視關係</t>
-  </si>
-  <si>
-    <t>只改變大小</t>
-  </si>
-  <si>
-    <t>不改變任何東西</t>
-  </si>
-  <si>
-    <t>仿射轉換矩陣的大小是？</t>
-  </si>
-  <si>
-    <t>2x2</t>
-  </si>
-  <si>
-    <t>5x5</t>
-  </si>
-  <si>
-    <t>4x4</t>
-  </si>
-  <si>
-    <t>3x3</t>
-  </si>
-  <si>
-    <t>齊次座標的目的是？</t>
-  </si>
-  <si>
-    <t>統一表示平移和其他轉換</t>
-  </si>
-  <si>
-    <t>減少記憶體</t>
-  </si>
-  <si>
-    <t>增加精度</t>
-  </si>
-  <si>
-    <t>簡化計算</t>
-  </si>
-  <si>
-    <t>最近鄰內插法的特點是？</t>
-  </si>
-  <si>
-    <t>記憶體需求大</t>
-  </si>
-  <si>
-    <t>速度快但品質較差</t>
-  </si>
-  <si>
-    <t>品質最好</t>
-  </si>
-  <si>
-    <t>計算複雜</t>
-  </si>
-  <si>
-    <t>雙線性內插法使用幾個鄰近像素？</t>
-  </si>
-  <si>
-    <t>1個</t>
-  </si>
-  <si>
-    <t>2個</t>
-  </si>
-  <si>
-    <t>4個</t>
-  </si>
-  <si>
-    <t>8個</t>
-  </si>
-  <si>
-    <t>雙三次內插法使用幾個鄰近像素？</t>
-  </si>
-  <si>
-    <t>16個</t>
-  </si>
-  <si>
-    <t>32個</t>
-  </si>
-  <si>
-    <t>影像放大時，最近鄰內插法會產生？</t>
-  </si>
-  <si>
-    <t>雜訊</t>
-  </si>
-  <si>
-    <t>鋸齒效果</t>
-  </si>
-  <si>
-    <t>失真</t>
-  </si>
-  <si>
-    <t>模糊效果</t>
-  </si>
-  <si>
-    <t>影像縮小時，容易產生什麼問題？</t>
-  </si>
-  <si>
-    <t>鋸齒</t>
-  </si>
-  <si>
-    <t>混疊效應</t>
-  </si>
-  <si>
-    <t>模糊</t>
-  </si>
-  <si>
-    <t>反混疊的方法是？</t>
-  </si>
-  <si>
-    <t>銳化</t>
-  </si>
-  <si>
-    <t>先平滑再降採樣</t>
-  </si>
-  <si>
-    <t>增加對比</t>
-  </si>
-  <si>
-    <t>增加解析度</t>
-  </si>
-  <si>
-    <t>影像旋轉後，空白區域通常填充？</t>
-  </si>
-  <si>
-    <t>黑色或指定顏色</t>
-  </si>
-  <si>
-    <t>鄰近像素</t>
-  </si>
-  <si>
-    <t>白色</t>
-  </si>
-  <si>
-    <t>隨機顏色</t>
-  </si>
-  <si>
-    <t>影像鏡像翻轉分為？</t>
-  </si>
-  <si>
-    <t>只有垂直翻轉</t>
-  </si>
-  <si>
-    <t>只有水平翻轉</t>
-  </si>
-  <si>
-    <t>水平和垂直翻轉</t>
-  </si>
-  <si>
-    <t>只有對角翻轉</t>
-  </si>
-  <si>
-    <t>影像剪切變換會產生？</t>
-  </si>
-  <si>
-    <t>縮放效果</t>
-  </si>
-  <si>
-    <t>旋轉效果</t>
-  </si>
-  <si>
-    <t>平移效果</t>
-  </si>
-  <si>
-    <t>傾斜效果</t>
-  </si>
-  <si>
-    <t>前向映射的問題是？</t>
-  </si>
-  <si>
-    <t>可能產生空洞</t>
-  </si>
-  <si>
-    <t>精度低</t>
-  </si>
-  <si>
-    <t>速度慢</t>
-  </si>
-  <si>
-    <t>後向映射的優點是？</t>
-  </si>
-  <si>
-    <t>計算簡單</t>
-  </si>
-  <si>
-    <t>不會產生空洞</t>
-  </si>
-  <si>
-    <t>記憶體少</t>
-  </si>
-  <si>
-    <t>速度快</t>
-  </si>
-  <si>
-    <t>影像配準的目的是？</t>
-  </si>
-  <si>
-    <t>壓縮影像</t>
-  </si>
-  <si>
-    <t>去除雜訊</t>
-  </si>
-  <si>
-    <t>對齊多張影像</t>
-  </si>
-  <si>
-    <t>增強對比</t>
-  </si>
-  <si>
-    <t>剛體轉換包括？</t>
-  </si>
-  <si>
-    <t>旋轉和縮放</t>
-  </si>
-  <si>
-    <t>平移和旋轉</t>
-  </si>
-  <si>
-    <t>所有轉換</t>
-  </si>
-  <si>
-    <t>平移和縮放</t>
-  </si>
-  <si>
-    <t>剛體轉換保持的性質是？</t>
-  </si>
-  <si>
-    <t>只保持角度</t>
-  </si>
-  <si>
-    <t>保持距離和角度</t>
-  </si>
-  <si>
-    <t>只保持距離</t>
-  </si>
-  <si>
-    <t>不保持任何性質</t>
-  </si>
-  <si>
-    <t>相似轉換包括？</t>
-  </si>
-  <si>
-    <t>平移、旋轉、等比縮放</t>
-  </si>
-  <si>
-    <t>平移、旋轉</t>
-  </si>
-  <si>
-    <t>透視轉換需要幾對對應點？</t>
-  </si>
-  <si>
-    <t>5對</t>
-  </si>
-  <si>
-    <t>4對</t>
-  </si>
-  <si>
-    <t>2對</t>
-  </si>
-  <si>
-    <t>3對</t>
-  </si>
-  <si>
-    <t>仿射轉換需要幾對對應點？</t>
-  </si>
-  <si>
-    <t>影像扭曲校正用於？</t>
-  </si>
-  <si>
-    <t>修正幾何失真</t>
-  </si>
-  <si>
-    <t>桶形失真的特徵是？</t>
-  </si>
-  <si>
-    <t>色彩失真</t>
-  </si>
-  <si>
-    <t>中心向內凹</t>
-  </si>
-  <si>
-    <t>中心向外凸</t>
-  </si>
-  <si>
-    <t>邊緣模糊</t>
-  </si>
-  <si>
-    <t>枕形失真的特徵是？</t>
-  </si>
-  <si>
-    <t>影像金字塔用於？</t>
-  </si>
-  <si>
-    <t>壓縮</t>
-  </si>
-  <si>
-    <t>多尺度處理</t>
-  </si>
-  <si>
-    <t>色彩轉換</t>
-  </si>
-  <si>
-    <t>雜訊去除</t>
-  </si>
-  <si>
-    <t>降採樣會？</t>
-  </si>
-  <si>
-    <t>減少解析度</t>
-  </si>
-  <si>
-    <t>不改變解析度</t>
-  </si>
-  <si>
-    <t>改變色彩</t>
-  </si>
-  <si>
-    <t>升採樣會？</t>
-  </si>
-  <si>
-    <t>影像拼接的關鍵步驟是？</t>
-  </si>
-  <si>
-    <t>只需旋轉</t>
-  </si>
-  <si>
-    <t>只需縮放</t>
-  </si>
-  <si>
-    <t>只需對齊</t>
-  </si>
-  <si>
-    <t>特徵匹配和融合</t>
-  </si>
-  <si>
-    <t>影像配準的方法包括？</t>
-  </si>
-  <si>
-    <t>只有手動配準</t>
-  </si>
-  <si>
-    <t>不需要配準</t>
-  </si>
-  <si>
-    <t>只有自動配準</t>
-  </si>
-  <si>
-    <t>手動和自動配準</t>
-  </si>
-  <si>
-    <t>特徵點匹配常用的特徵是？</t>
-  </si>
-  <si>
-    <t>顏色</t>
-  </si>
-  <si>
-    <t>角點和邊緣</t>
-  </si>
-  <si>
-    <t>紋理</t>
-  </si>
-  <si>
-    <t>亮度</t>
-  </si>
-  <si>
-    <t>SIFT特徵的特點是？</t>
-  </si>
-  <si>
-    <t>對旋轉和縮放不變</t>
-  </si>
-  <si>
-    <t>只對旋轉不變</t>
-  </si>
-  <si>
-    <t>對所有變換不變</t>
-  </si>
-  <si>
-    <t>只對縮放不變</t>
-  </si>
-  <si>
-    <t>影像變形（Morphing）是指？</t>
-  </si>
-  <si>
-    <t>影像旋轉</t>
-  </si>
-  <si>
-    <t>影像平移</t>
-  </si>
-  <si>
-    <t>影像之間的平滑過渡</t>
-  </si>
-  <si>
-    <t>影像縮放</t>
-  </si>
-  <si>
-    <t>影像校正的目的是？</t>
-  </si>
-  <si>
-    <t>消除幾何畸變</t>
-  </si>
-  <si>
-    <t>極座標轉換用於？</t>
-  </si>
-  <si>
-    <t>旋轉校正</t>
-  </si>
-  <si>
-    <t>縮放</t>
-  </si>
-  <si>
-    <t>平移</t>
-  </si>
-  <si>
-    <t>圓形物體展開</t>
-  </si>
-  <si>
-    <t>對數極座標的優點是？</t>
-  </si>
-  <si>
-    <t>旋轉和縮放轉為平移</t>
-  </si>
-  <si>
-    <t>精度高</t>
-  </si>
-  <si>
-    <t>影像重採樣的目的是？</t>
-  </si>
-  <si>
-    <t>改變影像解析度</t>
-  </si>
-  <si>
-    <t>Sinc內插法的特點是？</t>
-  </si>
-  <si>
-    <t>最簡單</t>
-  </si>
-  <si>
-    <t>理論上最佳</t>
-  </si>
-  <si>
-    <t>記憶體最少</t>
-  </si>
-  <si>
-    <t>速度最快</t>
-  </si>
-  <si>
-    <t>影像旋轉90度的特點是？</t>
-  </si>
-  <si>
-    <t>會模糊</t>
-  </si>
-  <si>
-    <t>需要內插</t>
-  </si>
-  <si>
-    <t>不需要內插</t>
-  </si>
-  <si>
-    <t>會失真</t>
-  </si>
-  <si>
-    <t>影像旋轉任意角度需要？</t>
-  </si>
-  <si>
-    <t>只需平移</t>
-  </si>
-  <si>
-    <t>影像縮放比例因子大於1表示？</t>
-  </si>
-  <si>
-    <t>不變</t>
-  </si>
-  <si>
-    <t>放大</t>
-  </si>
-  <si>
-    <t>縮小</t>
-  </si>
-  <si>
-    <t>旋轉</t>
-  </si>
-  <si>
-    <t>影像縮放比例因子小於1表示？</t>
-  </si>
-  <si>
-    <t>保持長寬比的縮放稱為？</t>
-  </si>
-  <si>
-    <t>等比縮放</t>
-  </si>
-  <si>
-    <t>非等比縮放</t>
-  </si>
-  <si>
-    <t>透視縮放</t>
-  </si>
-  <si>
-    <t>仿射縮放</t>
-  </si>
-  <si>
-    <t>不保持長寬比的縮放會？</t>
-  </si>
-  <si>
-    <t>保持形狀</t>
-  </si>
-  <si>
-    <t>改變形狀</t>
-  </si>
-  <si>
-    <t>保持角度</t>
-  </si>
-  <si>
-    <t>保持距離</t>
-  </si>
-  <si>
-    <t>影像的幾何不變矩用於？</t>
-  </si>
-  <si>
-    <t>形狀識別</t>
-  </si>
-  <si>
-    <t>邊緣檢測</t>
-  </si>
-  <si>
-    <t>色彩分析</t>
-  </si>
-  <si>
-    <t>Hu矩的特性是？</t>
-  </si>
-  <si>
-    <t>對平移、旋轉、縮放不變</t>
-  </si>
-  <si>
-    <t>只對平移不變</t>
-  </si>
-  <si>
-    <t>對所有變換敏感</t>
   </si>
   <si>
     <t>title</t>
@@ -674,8 +50,734 @@
     <t>chapter_name</t>
   </si>
   <si>
-    <t>CH 05-影像幾何轉換</t>
+    <t>對比度</t>
+  </si>
+  <si>
+    <t>壓縮影像檔案</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>保持不變</t>
+  </si>
+  <si>
+    <t>影像的寬度和高度</t>
+  </si>
+  <si>
+    <t>影像的寬度</t>
+  </si>
+  <si>
+    <t>不需要額外參數</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CH 05-影像幾何轉換 </t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙線性插值相較於最鄰近插值，主要改善了什麼問題？</t>
+  </si>
+  <si>
+    <t>計算速度</t>
+  </si>
+  <si>
+    <t>記憶體使用量</t>
+  </si>
+  <si>
+    <t>影像邊緣的鋸齒狀失真</t>
+  </si>
+  <si>
+    <t>檔案大小</t>
+  </si>
+  <si>
+    <t>在齊次座標系統中，平移矩陣右下角的元素通常設為多少？</t>
+  </si>
+  <si>
+    <t>tx</t>
+  </si>
+  <si>
+    <t>ty</t>
+  </si>
+  <si>
+    <t>在影像旋轉中，逆時針旋轉的角度θ通常如何表示？</t>
+  </si>
+  <si>
+    <t>正角度</t>
+  </si>
+  <si>
+    <t>負角度</t>
+  </si>
+  <si>
+    <t>零度</t>
+  </si>
+  <si>
+    <t>180度</t>
+  </si>
+  <si>
+    <t>相似變換相較於剛性變換，額外增加了什麼操作？</t>
+  </si>
+  <si>
+    <t>鏡像</t>
+  </si>
+  <si>
+    <t>轉置</t>
+  </si>
+  <si>
+    <t>傾斜</t>
+  </si>
+  <si>
+    <t>等距縮放</t>
+  </si>
+  <si>
+    <t>影像鏡像操作主要是反轉影像的什麼？</t>
+  </si>
+  <si>
+    <t>顏色通道</t>
+  </si>
+  <si>
+    <t>欄或列</t>
+  </si>
+  <si>
+    <t>解析度</t>
+  </si>
+  <si>
+    <t>繞任意點(a, b)旋轉的完整變換矩陣是由哪些矩陣相乘得到？</t>
+  </si>
+  <si>
+    <t>T1 × R</t>
+  </si>
+  <si>
+    <t>R × T2</t>
+  </si>
+  <si>
+    <t>T2 × R × T1</t>
+  </si>
+  <si>
+    <t>T1 × T2 × R</t>
+  </si>
+  <si>
+    <t>在影像縮放中，若sx = 2且sy = 2，影像會如何變化？</t>
+  </si>
+  <si>
+    <t>放大為原來的2倍</t>
+  </si>
+  <si>
+    <t>縮小為原來的1/4</t>
+  </si>
+  <si>
+    <t>放大為原來的4倍</t>
+  </si>
+  <si>
+    <t>影像校準(Image Registration)的主要目的是什麼？</t>
+  </si>
+  <si>
+    <t>增強影像對比度</t>
+  </si>
+  <si>
+    <t>轉換影像格式</t>
+  </si>
+  <si>
+    <t>將多個影像在空間上精確對齊</t>
+  </si>
+  <si>
+    <t>相似變換中的縮放比例s必須滿足什麼條件？</t>
+  </si>
+  <si>
+    <t>s可以是任意值</t>
+  </si>
+  <si>
+    <t>x和y方向的縮放比例必須相同</t>
+  </si>
+  <si>
+    <t>s必須大於1</t>
+  </si>
+  <si>
+    <t>s必須小於1</t>
+  </si>
+  <si>
+    <t>影像鏡像在深度學習中常用於什麼目的？</t>
+  </si>
+  <si>
+    <t>減少運算時間</t>
+  </si>
+  <si>
+    <t>提高影像解析度</t>
+  </si>
+  <si>
+    <t>壓縮模型大小</t>
+  </si>
+  <si>
+    <t>資料擴增以增加樣本多樣性</t>
+  </si>
+  <si>
+    <t>MATLAB的Camera Calibrator App建議使用多少張校準圖案影像？</t>
+  </si>
+  <si>
+    <t>3至5張</t>
+  </si>
+  <si>
+    <t>5至8張</t>
+  </si>
+  <si>
+    <t>10至20張</t>
+  </si>
+  <si>
+    <t>30至50張</t>
+  </si>
+  <si>
+    <t>以左上角為中心進行影像旋轉時，旋轉矩陣的主要元素包含什麼？</t>
+  </si>
+  <si>
+    <t>cos(θ)和sin(θ)</t>
+  </si>
+  <si>
+    <t>縮放因子sx和sy</t>
+  </si>
+  <si>
+    <t>平移量tx和ty</t>
+  </si>
+  <si>
+    <t>仿射轉換(Affine Transformation)具有什麼重要特性？</t>
+  </si>
+  <si>
+    <t>保持角度不變</t>
+  </si>
+  <si>
+    <t>保持距離不變</t>
+  </si>
+  <si>
+    <t>保持平行性</t>
+  </si>
+  <si>
+    <t>保持面積不變</t>
+  </si>
+  <si>
+    <t>齊次座標系統中，二維點(x, y)通常表示為幾維向量？</t>
+  </si>
+  <si>
+    <t>二維</t>
+  </si>
+  <si>
+    <t>三維</t>
+  </si>
+  <si>
+    <t>四維</t>
+  </si>
+  <si>
+    <t>五維</t>
+  </si>
+  <si>
+    <t>仿射轉換可以描述哪些幾何操作？</t>
+  </si>
+  <si>
+    <t>平移、旋轉、縮放和傾斜</t>
+  </si>
+  <si>
+    <t>僅縮放和旋轉</t>
+  </si>
+  <si>
+    <t>僅平移和旋轉</t>
+  </si>
+  <si>
+    <t>僅鏡像和轉置</t>
+  </si>
+  <si>
+    <t>汽車後視鏡使用影像鏡像的主要原因是什麼？</t>
+  </si>
+  <si>
+    <t>增加影像美觀度</t>
+  </si>
+  <si>
+    <t>減少運算負擔</t>
+  </si>
+  <si>
+    <t>讓駕駛更直觀地看到後方情況</t>
+  </si>
+  <si>
+    <t>剛性變換(Rigid Transformation)包含哪兩種基本操作？</t>
+  </si>
+  <si>
+    <t>縮放和旋轉</t>
+  </si>
+  <si>
+    <t>平移和旋轉</t>
+  </si>
+  <si>
+    <t>平移和縮放</t>
+  </si>
+  <si>
+    <t>旋轉和鏡像</t>
+  </si>
+  <si>
+    <t>影像水平鏡像後，像素座標(x, y)的x座標如何變化？（假設影像寬度為W）</t>
+  </si>
+  <si>
+    <t>x' = W - x</t>
+  </si>
+  <si>
+    <t>x' = x</t>
+  </si>
+  <si>
+    <t>x' = -x</t>
+  </si>
+  <si>
+    <t>x' = x + W</t>
+  </si>
+  <si>
+    <t>三次立方插值相較於雙線性插值，主要優勢是什麼？</t>
+  </si>
+  <si>
+    <t>計算速度更快</t>
+  </si>
+  <si>
+    <t>記憶體使用更少</t>
+  </si>
+  <si>
+    <t>可以獲得更好的影像品質</t>
+  </si>
+  <si>
+    <t>影像幾何轉換主要是對影像的哪一個特性進行轉換？</t>
+  </si>
+  <si>
+    <t>顏色與亮度</t>
+  </si>
+  <si>
+    <t>壓縮比率</t>
+  </si>
+  <si>
+    <t>檔案格式</t>
+  </si>
+  <si>
+    <t>空間座標</t>
+  </si>
+  <si>
+    <t>在相機內部參數矩陣中，fx = f / Ix這個公式中，f代表什麼？</t>
+  </si>
+  <si>
+    <t>相機的焦距</t>
+  </si>
+  <si>
+    <t>像素的大小</t>
+  </si>
+  <si>
+    <t>主點的x座標</t>
+  </si>
+  <si>
+    <t>影像轉置後，原本左上角的像素會移動到哪裡？</t>
+  </si>
+  <si>
+    <t>右上角</t>
+  </si>
+  <si>
+    <t>左下角</t>
+  </si>
+  <si>
+    <t>右下角</t>
+  </si>
+  <si>
+    <t>影像幾何轉換後可能導致某些像素被丟棄，這時需要使用什麼技術？</t>
+  </si>
+  <si>
+    <t>色彩校正</t>
+  </si>
+  <si>
+    <t>邊緣檢測</t>
+  </si>
+  <si>
+    <t>直方圖均衡化</t>
+  </si>
+  <si>
+    <t>插值方法</t>
+  </si>
+  <si>
+    <t>相機幾何失真主要分為哪兩類參數造成的失真？</t>
+  </si>
+  <si>
+    <t>內部參數和外部參數</t>
+  </si>
+  <si>
+    <t>顏色參數和亮度參數</t>
+  </si>
+  <si>
+    <t>軟體參數和硬體參數</t>
+  </si>
+  <si>
+    <t>靜態參數和動態參數</t>
+  </si>
+  <si>
+    <t>以左上角為中心逆時針旋轉θ度時，新座標x'的完整公式是？</t>
+  </si>
+  <si>
+    <t>x' = x*cos(θ) + y*sin(θ)</t>
+  </si>
+  <si>
+    <t>x' = x*cos(θ) - y*sin(θ)</t>
+  </si>
+  <si>
+    <t>x' = x*sin(θ) + y*cos(θ)</t>
+  </si>
+  <si>
+    <t>x' = x*sin(θ) - y*cos(θ)</t>
+  </si>
+  <si>
+    <t>在相機內部參數矩陣K中，fx和fy代表什麼？</t>
+  </si>
+  <si>
+    <t>x和y方向的焦距（以像素為單位）</t>
+  </si>
+  <si>
+    <t>主點的座標</t>
+  </si>
+  <si>
+    <t>鏡頭的畸變係數</t>
+  </si>
+  <si>
+    <t>剛性變換保持什麼不變？</t>
+  </si>
+  <si>
+    <t>顏色和亮度</t>
+  </si>
+  <si>
+    <t>形狀和大小</t>
+  </si>
+  <si>
+    <t>在平移矩陣中，tx和ty分別代表什麼？</t>
+  </si>
+  <si>
+    <t>旋轉角度和縮放比例</t>
+  </si>
+  <si>
+    <t>像素的顏色值</t>
+  </si>
+  <si>
+    <t>x方向和y方向的位移量</t>
+  </si>
+  <si>
+    <t>以任意點(a, b)為中心進行旋轉需要幾個步驟？</t>
+  </si>
+  <si>
+    <t>一個步驟：直接旋轉</t>
+  </si>
+  <si>
+    <t>兩個步驟：平移和旋轉</t>
+  </si>
+  <si>
+    <t>三個步驟：平移、旋轉、反平移</t>
+  </si>
+  <si>
+    <t>四個步驟：平移、旋轉、縮放、反平移</t>
+  </si>
+  <si>
+    <t>最鄰近插值的數學表達式f(x, y) = f(round(nx), round(ny))中，n代表什麼？</t>
+  </si>
+  <si>
+    <t>影像的總像素數</t>
+  </si>
+  <si>
+    <t>縮放比例</t>
+  </si>
+  <si>
+    <t>旋轉角度</t>
+  </si>
+  <si>
+    <t>平移距離</t>
+  </si>
+  <si>
+    <t>在相似變換矩陣中，如果s=0.5且θ=90度，影像會發生什麼變化？</t>
+  </si>
+  <si>
+    <t>放大2倍並順時針旋轉90度</t>
+  </si>
+  <si>
+    <t>放大2倍並逆時針旋轉90度</t>
+  </si>
+  <si>
+    <t>縮小為1/2並順時針旋轉90度</t>
+  </si>
+  <si>
+    <t>縮小為1/2並逆時針旋轉90度</t>
+  </si>
+  <si>
+    <t>影像轉置操作實際上是將矩陣的什麼互換？</t>
+  </si>
+  <si>
+    <t>行和列</t>
+  </si>
+  <si>
+    <t>像素值</t>
+  </si>
+  <si>
+    <t>座標系統</t>
+  </si>
+  <si>
+    <t>Registration Estimator App中，Moving影像指的是什麼？</t>
+  </si>
+  <si>
+    <t>標準參考影像</t>
+  </si>
+  <si>
+    <t>要進行矩陣轉換的影像</t>
+  </si>
+  <si>
+    <t>已經校準完成的影像</t>
+  </si>
+  <si>
+    <t>原始未處理的影像</t>
+  </si>
+  <si>
+    <t>仿射轉換矩陣中，哪兩個參數主要描述傾斜(shear)操作？</t>
+  </si>
+  <si>
+    <t>(a, e)</t>
+  </si>
+  <si>
+    <t>(g, h)</t>
+  </si>
+  <si>
+    <t>(b, d)</t>
+  </si>
+  <si>
+    <t>(c, f)</t>
+  </si>
+  <si>
+    <t>相機的內部參數主要描述什麼？</t>
+  </si>
+  <si>
+    <t>相機在世界座標系中的位置</t>
+  </si>
+  <si>
+    <t>影像的壓縮率</t>
+  </si>
+  <si>
+    <t>影像的色彩空間</t>
+  </si>
+  <si>
+    <t>相機的幾何和光學特性</t>
+  </si>
+  <si>
+    <t>在Registration Estimator App中，如果輸入的是彩色影像，系統會如何處理？</t>
+  </si>
+  <si>
+    <t>自動轉換為灰階影像</t>
+  </si>
+  <si>
+    <t>拒絕處理並報錯</t>
+  </si>
+  <si>
+    <t>直接使用彩色影像進行校準</t>
+  </si>
+  <si>
+    <t>只使用紅色通道</t>
+  </si>
+  <si>
+    <t>為什麼多種幾何變換可以通過矩陣乘法輕易結合？</t>
+  </si>
+  <si>
+    <t>因為使用了齊次座標系統</t>
+  </si>
+  <si>
+    <t>因為使用了極座標系統</t>
+  </si>
+  <si>
+    <t>因為使用了球面座標系統</t>
+  </si>
+  <si>
+    <t>因為使用了笛卡爾座標系統</t>
+  </si>
+  <si>
+    <t>在影像平移操作中，主要改變的是像素的什麼特性？</t>
+  </si>
+  <si>
+    <t>顏色值</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>亮度</t>
+  </si>
+  <si>
+    <t>仿射轉換矩陣有幾個自由參數？</t>
+  </si>
+  <si>
+    <t>3個</t>
+  </si>
+  <si>
+    <t>4個</t>
+  </si>
+  <si>
+    <t>6個</t>
+  </si>
+  <si>
+    <t>9個</t>
+  </si>
+  <si>
+    <t>在影像校準中，Fixed影像的作用是什麼？</t>
+  </si>
+  <si>
+    <t>需要被校正的影像</t>
+  </si>
+  <si>
+    <t>需要被壓縮的影像</t>
+  </si>
+  <si>
+    <t>已經失真的影像</t>
+  </si>
+  <si>
+    <t>作為標準參考的影像</t>
+  </si>
+  <si>
+    <t>影像轉置操作是沿著什麼線交換像素位置？</t>
+  </si>
+  <si>
+    <t>水平中線</t>
+  </si>
+  <si>
+    <t>垂直中線</t>
+  </si>
+  <si>
+    <t>主對角線</t>
+  </si>
+  <si>
+    <t>副對角線</t>
+  </si>
+  <si>
+    <t>在影像旋轉中，如果要繞任意點(a, b)旋轉，第一步需要做什麼？</t>
+  </si>
+  <si>
+    <t>直接旋轉影像</t>
+  </si>
+  <si>
+    <t>將旋轉中心平移到原點</t>
+  </si>
+  <si>
+    <t>縮放影像</t>
+  </si>
+  <si>
+    <t>鏡像影像</t>
+  </si>
+  <si>
+    <t>在影像縮放中，縮放矩陣通常使用什麼座標系統來表示？</t>
+  </si>
+  <si>
+    <t>笛卡爾座標</t>
+  </si>
+  <si>
+    <t>極座標</t>
+  </si>
+  <si>
+    <t>球面座標</t>
+  </si>
+  <si>
+    <t>齊次座標</t>
+  </si>
+  <si>
+    <t>下列哪一種插值方法計算量最大但品質最好？</t>
+  </si>
+  <si>
+    <t>三次立方插值</t>
+  </si>
+  <si>
+    <t>雙線性插值</t>
+  </si>
+  <si>
+    <t>最鄰近插值</t>
+  </si>
+  <si>
+    <t>線性插值</t>
+  </si>
+  <si>
+    <t>相機的外部參數主要由哪兩個矩陣組成？</t>
+  </si>
+  <si>
+    <t>縮放矩陣和平移矩陣</t>
+  </si>
+  <si>
+    <t>旋轉矩陣和平移向量</t>
+  </si>
+  <si>
+    <t>鏡像矩陣和旋轉矩陣</t>
+  </si>
+  <si>
+    <t>內部矩陣和外部矩陣</t>
+  </si>
+  <si>
+    <t>在影像幾何轉換中，為什麼需要插值方法？</t>
+  </si>
+  <si>
+    <t>為了增加影像對比度</t>
+  </si>
+  <si>
+    <t>為了改變色彩空間</t>
+  </si>
+  <si>
+    <t>為了壓縮影像檔案</t>
+  </si>
+  <si>
+    <t>為了處理轉換後的非整數座標</t>
+  </si>
+  <si>
+    <t>MATLAB中用於相機校正的工具是什麼？</t>
+  </si>
+  <si>
+    <t>Image Processing Toolbox</t>
+  </si>
+  <si>
+    <t>Deep Learning Toolbox</t>
+  </si>
+  <si>
+    <t>Camera Calibrator App</t>
+  </si>
+  <si>
+    <t>Computer Vision Toolbox</t>
+  </si>
+  <si>
+    <t>下列何者不是影像幾何轉換的主要目的？</t>
+  </si>
+  <si>
+    <t>改變影像色彩</t>
+  </si>
+  <si>
+    <t>調整影像尺寸</t>
+  </si>
+  <si>
+    <t>校正影像畸變</t>
+  </si>
+  <si>
+    <t>旋轉影像角度</t>
+  </si>
+  <si>
+    <t>最鄰近插值法的主要優點是什麼？</t>
+  </si>
+  <si>
+    <t>影像品質最佳</t>
+  </si>
+  <si>
+    <t>計算速度快</t>
+  </si>
+  <si>
+    <t>細節保留完整</t>
+  </si>
+  <si>
+    <t>無失真</t>
+  </si>
+  <si>
+    <t>在齊次座標系統中，點P(x, y)經過平移矩陣T變換後，新座標x'的計算公式是？</t>
+  </si>
+  <si>
+    <t>x' = x * tx</t>
+  </si>
+  <si>
+    <t>x' = tx / x</t>
+  </si>
+  <si>
+    <t>x' = x - tx</t>
+  </si>
+  <si>
+    <t>x' = x + tx</t>
   </si>
 </sst>
 </file>
@@ -1041,19 +1143,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="74.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>215</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -1078,39 +1188,39 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1118,119 +1228,119 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -1238,59 +1348,59 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -1298,19 +1408,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1318,39 +1428,39 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1358,219 +1468,219 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -1578,99 +1688,99 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -1678,119 +1788,119 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1798,119 +1908,119 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="E44" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -1918,59 +2028,59 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C45" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="E45" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F47">
         <v>2</v>
@@ -1978,102 +2088,102 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D48" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="E48" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="B50" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="B52" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="C52" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="D52" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
